--- a/labels.xlsx
+++ b/labels.xlsx
@@ -24,103 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
-  <si>
-    <t>Těžba a dobývání</t>
-  </si>
-  <si>
-    <t>Těžba a úprava černého a hnědého uhlí</t>
-  </si>
-  <si>
-    <t>Těžba ropy a zemního plynu</t>
-  </si>
-  <si>
-    <t>Těžba a úprava rud</t>
-  </si>
-  <si>
-    <t>Ostatní těžba a dobývání</t>
-  </si>
-  <si>
-    <t>Podpůrné činnosti při těžbě</t>
-  </si>
-  <si>
-    <t>Zpracovatelský průmysl</t>
-  </si>
-  <si>
-    <t>Výroba potravinářských výrobků</t>
-  </si>
-  <si>
-    <t>Výroba nápojů</t>
-  </si>
-  <si>
-    <t>Výroba tabákových výrobků</t>
-  </si>
-  <si>
-    <t>Výroba textilií</t>
-  </si>
-  <si>
-    <t>Výroba oděvů</t>
-  </si>
-  <si>
-    <t>Výroba usní a souvisejících výrobků</t>
-  </si>
-  <si>
-    <t>Zpracování dřeva, výroba dřevěných, korkových, proutěných a slaměných výrobků, kromě nábytku</t>
-  </si>
-  <si>
-    <t>Výroba papíru a výrobků z papíru</t>
-  </si>
-  <si>
-    <t>Tisk a rozmnožování nahraných nosičů</t>
-  </si>
-  <si>
-    <t>Výroba koksu a rafinovaných ropných produktů</t>
-  </si>
-  <si>
-    <t>Výroba chemických látek a chemických přípravků</t>
-  </si>
-  <si>
-    <t>Výroba základních farmaceutických výrobků a farmaceutických přípravků</t>
-  </si>
-  <si>
-    <t>Výroba pryžových a plastových výrobků</t>
-  </si>
-  <si>
-    <t>Výroba ostatních nekovových minerálních výrobků</t>
-  </si>
-  <si>
-    <t>Výroba základních kovů, hutní zpracování; slévárenství</t>
-  </si>
-  <si>
-    <t>Výroba kovových konstrukci a kovodělných výrobků, kromě strojů a zařízení</t>
-  </si>
-  <si>
-    <t>Výroba počítačů, elektronických a optických přístrojů a zařízení</t>
-  </si>
-  <si>
-    <t>Výroba elektrických  zařízení</t>
-  </si>
-  <si>
-    <t>Výroba strojů a  zařízení, j.n.</t>
-  </si>
-  <si>
-    <t>Výroba motorových vozidel (kromě motocyklů), přívěsu a návěsu</t>
-  </si>
-  <si>
-    <t>Výroba ostatních dopravních prostředků a zařízení</t>
-  </si>
-  <si>
-    <t>Výroba nábytku</t>
-  </si>
-  <si>
-    <t>Ostatní zpracovatelský průmysl</t>
-  </si>
-  <si>
-    <t>Opravy a instalace strojů a zařízení</t>
-  </si>
-  <si>
-    <t>Výroba a rozvod elektřiny, plynu, tepla a klimatizovaného vzduchu</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -230,7 +134,106 @@
     <t>pr</t>
   </si>
   <si>
-    <t>Průmysl celkem</t>
+    <t>B - Těžba a dobývání</t>
+  </si>
+  <si>
+    <t>05 - Těžba a úprava černého a hnědého uhlí</t>
+  </si>
+  <si>
+    <t>06 - Těžba ropy a zemního plynu</t>
+  </si>
+  <si>
+    <t>07 - Těžba a úprava rud</t>
+  </si>
+  <si>
+    <t>08 - Ostatní těžba a dobývání</t>
+  </si>
+  <si>
+    <t>09 - Podpůrné činnosti při těžbě</t>
+  </si>
+  <si>
+    <t>C - Zpracovatelský průmysl</t>
+  </si>
+  <si>
+    <t>10 - Výroba potravinářských výrobků</t>
+  </si>
+  <si>
+    <t>11 - Výroba nápojů</t>
+  </si>
+  <si>
+    <t>12 - Výroba tabákových výrobků</t>
+  </si>
+  <si>
+    <t>13 - Výroba textilií</t>
+  </si>
+  <si>
+    <t>14 - Výroba oděvů</t>
+  </si>
+  <si>
+    <t>15 - Výroba usní a souvisejících výrobků</t>
+  </si>
+  <si>
+    <t>16 - Zpracování dřeva, výroba dřevěných, korkových, proutěných a slaměných výrobků, kromě nábytku</t>
+  </si>
+  <si>
+    <t>17 - Výroba papíru a výrobků z papíru</t>
+  </si>
+  <si>
+    <t>18 - Tisk a rozmnožování nahraných nosičů</t>
+  </si>
+  <si>
+    <t>19 - Výroba koksu a rafinovaných ropných produktů</t>
+  </si>
+  <si>
+    <t>20 - Výroba chemických látek a chemických přípravků</t>
+  </si>
+  <si>
+    <t>21 - Výroba základních farmaceutických výrobků a farmaceutických přípravků</t>
+  </si>
+  <si>
+    <t>22 - Výroba pryžových a plastových výrobků</t>
+  </si>
+  <si>
+    <t>23  - Výroba ostatních nekovových minerálních výrobků</t>
+  </si>
+  <si>
+    <t>24 - Výroba základních kovů, hutní zpracování; slévárenství</t>
+  </si>
+  <si>
+    <t>25 - Výroba kovových konstrukci a kovodělných výrobků, kromě strojů a zařízení</t>
+  </si>
+  <si>
+    <t>26 - Výroba počítačů, elektronických a optických přístrojů a zařízení</t>
+  </si>
+  <si>
+    <t>27 - Výroba elektrických  zařízení</t>
+  </si>
+  <si>
+    <t>28 - Výroba strojů a  zařízení, j.n.</t>
+  </si>
+  <si>
+    <t>29 - Výroba motorových vozidel (kromě motocyklů), přívěsu a návěsu</t>
+  </si>
+  <si>
+    <t>30 - Výroba ostatních dopravních prostředků a zařízení</t>
+  </si>
+  <si>
+    <t>31 - Výroba nábytku</t>
+  </si>
+  <si>
+    <t>32 - Ostatní zpracovatelský průmysl</t>
+  </si>
+  <si>
+    <t>33 - Opravy a instalace strojů a zařízení</t>
+  </si>
+  <si>
+    <t>D - Výroba a rozvod elektřiny, plynu, tepla a klimatizovaného vzduchu</t>
+  </si>
+  <si>
+    <t>35 - Výroba a rozvod elektřiny, plynu, tepla a klimatizovaného vzduchu</t>
+  </si>
+  <si>
+    <t>B+C+D - Průmysl celkem</t>
   </si>
 </sst>
 </file>
@@ -554,282 +557,282 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/labels.xlsx
+++ b/labels.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="82">
   <si>
     <t>id</t>
   </si>
@@ -234,6 +234,42 @@
   </si>
   <si>
     <t>B+C+D - Průmysl celkem</t>
+  </si>
+  <si>
+    <t>celkem</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>id_p</t>
+  </si>
+  <si>
+    <t>id_z</t>
+  </si>
+  <si>
+    <t>id_t</t>
   </si>
 </sst>
 </file>
@@ -270,8 +306,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -552,286 +589,601 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>14</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>17</v>
+      </c>
+      <c r="D17">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>18</v>
+      </c>
+      <c r="C18">
+        <v>18</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>19</v>
+      </c>
+      <c r="C19">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>21</v>
+      </c>
+      <c r="C21">
+        <v>21</v>
+      </c>
+      <c r="D21">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22">
+        <v>22</v>
+      </c>
+      <c r="C22">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>22</v>
+      </c>
+      <c r="E22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <v>23</v>
+      </c>
+      <c r="D23">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24">
+        <v>24</v>
+      </c>
+      <c r="C24">
+        <v>24</v>
+      </c>
+      <c r="D24">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>25</v>
+      </c>
+      <c r="D25">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26">
+        <v>26</v>
+      </c>
+      <c r="C26">
+        <v>26</v>
+      </c>
+      <c r="D26">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27">
+        <v>27</v>
+      </c>
+      <c r="C27">
+        <v>27</v>
+      </c>
+      <c r="D27">
+        <v>27</v>
+      </c>
+      <c r="E27" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28">
+        <v>28</v>
+      </c>
+      <c r="C28">
+        <v>28</v>
+      </c>
+      <c r="D28">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29">
+        <v>29</v>
+      </c>
+      <c r="C29">
+        <v>29</v>
+      </c>
+      <c r="D29">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30">
+        <v>30</v>
+      </c>
+      <c r="C30">
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31">
+        <v>31</v>
+      </c>
+      <c r="C31">
+        <v>31</v>
+      </c>
+      <c r="D31">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32">
+        <v>32</v>
+      </c>
+      <c r="C32">
+        <v>32</v>
+      </c>
+      <c r="D32">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33">
+        <v>33</v>
+      </c>
+      <c r="C33">
+        <v>33</v>
+      </c>
+      <c r="D33">
+        <v>33</v>
+      </c>
+      <c r="E33" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35">
+        <v>35</v>
+      </c>
+      <c r="C35">
+        <v>35</v>
+      </c>
+      <c r="D35">
+        <v>35</v>
+      </c>
+      <c r="E35" t="s">
         <v>68</v>
       </c>
     </row>
